--- a/test/customer-journey/CosmoEdge-主要功能客户旅程测试用例.xlsx
+++ b/test/customer-journey/CosmoEdge-主要功能客户旅程测试用例.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="评审总览" sheetId="1" r:id="R50abca8c7092439a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要用例" sheetId="2" r:id="R56cf9666b22348bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="步骤与验收" sheetId="3" r:id="R0820840be99b4cc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="按需补测" sheetId="4" r:id="Ra60342abbb694fb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="范围与评审" sheetId="5" r:id="Rce831478a36b44a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="评审总览" sheetId="1" r:id="R4e2e12dec86c44b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要用例" sheetId="2" r:id="Reb05f24b4b734d80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="步骤与验收" sheetId="3" r:id="R23f294e649194cb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="按需补测" sheetId="4" r:id="Ra763ecfcb5974a60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="范围与评审" sheetId="5" r:id="R9023807993d24ff5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -146,7 +146,7 @@
         <x:color rgb="FF9A3412"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4E4"/>
         </x:patternFill>
       </x:fill>
@@ -157,7 +157,7 @@
         <x:color rgb="FF9A3412"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0D5"/>
         </x:patternFill>
       </x:fill>
@@ -168,7 +168,7 @@
         <x:color rgb="FF9A3412"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0D5"/>
         </x:patternFill>
       </x:fill>
@@ -178,8 +178,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="QuickCases" displayName="QuickCases" ref="A4:L32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:L32"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="QuickCases" displayName="QuickCases" ref="A4:L33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:L33"/>
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="模块"/>
@@ -199,8 +199,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="QuickSteps" displayName="QuickSteps" ref="A4:I99" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:I99"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="QuickSteps" displayName="QuickSteps" ref="A4:I106" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:I106"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="用例编号"/>
     <x:tableColumn id="2" name="步骤编号"/>
@@ -472,7 +472,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="16" t="str">
-        <x:v>v0.5 已确认快测用例 · 2026-10-14 · 尚未执行设备测试</x:v>
+        <x:v>v0.7 已确认快测用例 · 2026-10-19 · 用例定义，实测结果另存</x:v>
       </x:c>
       <x:c r="B3" s="3"/>
       <x:c r="C3" s="3"/>
@@ -493,15 +493,15 @@
         <x:v>核心用例数</x:v>
       </x:c>
       <x:c r="B5" s="3" t="n">
-        <x:f>COUNTA('主要用例'!A5:A32)</x:f>
-        <x:v>28</x:v>
+        <x:f>COUNTA('主要用例'!A5:A33)</x:f>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C5" s="3"/>
       <x:c r="D5" s="3" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="E5" s="3" t="n">
-        <x:f>COUNTIFS('主要用例'!J5:J32,"通过")</x:f>
+        <x:f>COUNTIFS('主要用例'!J5:J33,"通过")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="15" t="str">
@@ -513,14 +513,14 @@
         <x:v>逐步验收数</x:v>
       </x:c>
       <x:c r="B6" s="3" t="n">
-        <x:v>95</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C6" s="3"/>
       <x:c r="D6" s="3" t="str">
         <x:v>失败</x:v>
       </x:c>
       <x:c r="E6" s="3" t="n">
-        <x:f>COUNTIFS('主要用例'!J5:J32,"失败")</x:f>
+        <x:f>COUNTIFS('主要用例'!J5:J33,"失败")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F6" s="15" t="str">
@@ -532,15 +532,15 @@
         <x:v>预计正常下限（分钟）</x:v>
       </x:c>
       <x:c r="B7" s="3" t="n">
-        <x:f>SUM('主要用例'!F5:F32)</x:f>
-        <x:v>141</x:v>
+        <x:f>SUM('主要用例'!F5:F33)</x:f>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C7" s="3"/>
       <x:c r="D7" s="3" t="str">
         <x:v>阻塞</x:v>
       </x:c>
       <x:c r="E7" s="3" t="n">
-        <x:f>COUNTIFS('主要用例'!J5:J32,"阻塞")</x:f>
+        <x:f>COUNTIFS('主要用例'!J5:J33,"阻塞")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F7" s="3" t="str">
@@ -552,15 +552,15 @@
         <x:v>预计正常上限（分钟）</x:v>
       </x:c>
       <x:c r="B8" s="3" t="n">
-        <x:f>SUM('主要用例'!G5:G32)</x:f>
-        <x:v>232</x:v>
+        <x:f>SUM('主要用例'!G5:G33)</x:f>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C8" s="3"/>
       <x:c r="D8" s="3" t="str">
         <x:v>部分完成</x:v>
       </x:c>
       <x:c r="E8" s="3" t="n">
-        <x:f>COUNTIFS('主要用例'!J5:J32,"部分完成")</x:f>
+        <x:f>COUNTIFS('主要用例'!J5:J33,"部分完成")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F8" s="3" t="str">
@@ -579,8 +579,8 @@
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="E9" s="3" t="n">
-        <x:f>COUNTIFS('主要用例'!J5:J32,"未执行")</x:f>
-        <x:v>28</x:v>
+        <x:f>COUNTIFS('主要用例'!J5:J33,"未执行")</x:f>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F9" s="3"/>
     </x:row>
@@ -592,7 +592,7 @@
         <x:v>不适用</x:v>
       </x:c>
       <x:c r="E10" s="3" t="n">
-        <x:f>COUNTIFS('主要用例'!J5:J32,"不适用")</x:f>
+        <x:f>COUNTIFS('主要用例'!J5:J33,"不适用")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F10" s="3"/>
@@ -620,15 +620,15 @@
         <x:v>准备与登录</x:v>
       </x:c>
       <x:c r="B12" s="3" t="n">
-        <x:f>COUNTIFS('主要用例'!B5:B32,A12)</x:f>
+        <x:f>COUNTIFS('主要用例'!B5:B33,A12)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C12" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!F5:F32,'主要用例'!B5:B32,A12)</x:f>
+        <x:f>SUMIFS('主要用例'!F5:F33,'主要用例'!B5:B33,A12)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="D12" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!G5:G32,'主要用例'!B5:B32,A12)</x:f>
+        <x:f>SUMIFS('主要用例'!G5:G33,'主要用例'!B5:B33,A12)</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="E12" s="3"/>
@@ -641,15 +641,15 @@
         <x:v>模型与场景</x:v>
       </x:c>
       <x:c r="B13" s="3" t="n">
-        <x:f>COUNTIFS('主要用例'!B5:B32,A13)</x:f>
+        <x:f>COUNTIFS('主要用例'!B5:B33,A13)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C13" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!F5:F32,'主要用例'!B5:B32,A13)</x:f>
+        <x:f>SUMIFS('主要用例'!F5:F33,'主要用例'!B5:B33,A13)</x:f>
         <x:v>11</x:v>
       </x:c>
       <x:c r="D13" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!G5:G32,'主要用例'!B5:B32,A13)</x:f>
+        <x:f>SUMIFS('主要用例'!G5:G33,'主要用例'!B5:B33,A13)</x:f>
         <x:v>18</x:v>
       </x:c>
       <x:c r="E13" s="3"/>
@@ -662,15 +662,15 @@
         <x:v>视频接入</x:v>
       </x:c>
       <x:c r="B14" s="3" t="n">
-        <x:f>COUNTIFS('主要用例'!B5:B32,A14)</x:f>
+        <x:f>COUNTIFS('主要用例'!B5:B33,A14)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="C14" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!F5:F32,'主要用例'!B5:B32,A14)</x:f>
+        <x:f>SUMIFS('主要用例'!F5:F33,'主要用例'!B5:B33,A14)</x:f>
         <x:v>29</x:v>
       </x:c>
       <x:c r="D14" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!G5:G32,'主要用例'!B5:B32,A14)</x:f>
+        <x:f>SUMIFS('主要用例'!G5:G33,'主要用例'!B5:B33,A14)</x:f>
         <x:v>46</x:v>
       </x:c>
       <x:c r="E14" s="3"/>
@@ -683,15 +683,15 @@
         <x:v>任务与规则</x:v>
       </x:c>
       <x:c r="B15" s="3" t="n">
-        <x:f>COUNTIFS('主要用例'!B5:B32,A15)</x:f>
+        <x:f>COUNTIFS('主要用例'!B5:B33,A15)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C15" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!F5:F32,'主要用例'!B5:B32,A15)</x:f>
+        <x:f>SUMIFS('主要用例'!F5:F33,'主要用例'!B5:B33,A15)</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="D15" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!G5:G32,'主要用例'!B5:B32,A15)</x:f>
+        <x:f>SUMIFS('主要用例'!G5:G33,'主要用例'!B5:B33,A15)</x:f>
         <x:v>16</x:v>
       </x:c>
       <x:c r="E15" s="3"/>
@@ -704,15 +704,15 @@
         <x:v>底库与识别</x:v>
       </x:c>
       <x:c r="B16" s="3" t="n">
-        <x:f>COUNTIFS('主要用例'!B5:B32,A16)</x:f>
+        <x:f>COUNTIFS('主要用例'!B5:B33,A16)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="C16" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!F5:F32,'主要用例'!B5:B32,A16)</x:f>
+        <x:f>SUMIFS('主要用例'!F5:F33,'主要用例'!B5:B33,A16)</x:f>
         <x:v>16</x:v>
       </x:c>
       <x:c r="D16" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!G5:G32,'主要用例'!B5:B32,A16)</x:f>
+        <x:f>SUMIFS('主要用例'!G5:G33,'主要用例'!B5:B33,A16)</x:f>
         <x:v>26</x:v>
       </x:c>
       <x:c r="E16" s="3"/>
@@ -725,15 +725,15 @@
         <x:v>图片分析</x:v>
       </x:c>
       <x:c r="B17" s="3" t="n">
-        <x:f>COUNTIFS('主要用例'!B5:B32,A17)</x:f>
+        <x:f>COUNTIFS('主要用例'!B5:B33,A17)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="C17" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!F5:F32,'主要用例'!B5:B32,A17)</x:f>
+        <x:f>SUMIFS('主要用例'!F5:F33,'主要用例'!B5:B33,A17)</x:f>
         <x:v>13</x:v>
       </x:c>
       <x:c r="D17" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!G5:G32,'主要用例'!B5:B32,A17)</x:f>
+        <x:f>SUMIFS('主要用例'!G5:G33,'主要用例'!B5:B33,A17)</x:f>
         <x:v>21</x:v>
       </x:c>
       <x:c r="E17" s="3"/>
@@ -746,15 +746,15 @@
         <x:v>大模型算法</x:v>
       </x:c>
       <x:c r="B18" s="3" t="n">
-        <x:f>COUNTIFS('主要用例'!B5:B32,A18)</x:f>
+        <x:f>COUNTIFS('主要用例'!B5:B33,A18)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C18" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!F5:F32,'主要用例'!B5:B32,A18)</x:f>
+        <x:f>SUMIFS('主要用例'!F5:F33,'主要用例'!B5:B33,A18)</x:f>
         <x:v>22</x:v>
       </x:c>
       <x:c r="D18" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!G5:G32,'主要用例'!B5:B32,A18)</x:f>
+        <x:f>SUMIFS('主要用例'!G5:G33,'主要用例'!B5:B33,A18)</x:f>
         <x:v>40</x:v>
       </x:c>
       <x:c r="E18" s="3"/>
@@ -767,20 +767,20 @@
         <x:v>事件与展示</x:v>
       </x:c>
       <x:c r="B19" s="3" t="n">
-        <x:f>COUNTIFS('主要用例'!B5:B32,A19)</x:f>
-        <x:v>3</x:v>
+        <x:f>COUNTIFS('主要用例'!B5:B33,A19)</x:f>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C19" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!F5:F32,'主要用例'!B5:B32,A19)</x:f>
-        <x:v>13</x:v>
+        <x:f>SUMIFS('主要用例'!F5:F33,'主要用例'!B5:B33,A19)</x:f>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D19" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!G5:G32,'主要用例'!B5:B32,A19)</x:f>
-        <x:v>22</x:v>
+        <x:f>SUMIFS('主要用例'!G5:G33,'主要用例'!B5:B33,A19)</x:f>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E19" s="3"/>
       <x:c r="F19" s="3" t="str">
-        <x:v>单/四窗预览与叠加；新告警详情；首页统计核对。</x:v>
+        <x:v>单/四窗预览与叠加；新告警详情；事件上报本地/接口大模型审核；首页统计。</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="38" customHeight="1">
@@ -788,20 +788,20 @@
         <x:v>数据对接</x:v>
       </x:c>
       <x:c r="B20" s="3" t="n">
-        <x:f>COUNTIFS('主要用例'!B5:B32,A20)</x:f>
+        <x:f>COUNTIFS('主要用例'!B5:B33,A20)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C20" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!F5:F32,'主要用例'!B5:B32,A20)</x:f>
+        <x:f>SUMIFS('主要用例'!F5:F33,'主要用例'!B5:B33,A20)</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="D20" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!G5:G32,'主要用例'!B5:B32,A20)</x:f>
+        <x:f>SUMIFS('主要用例'!G5:G33,'主要用例'!B5:B33,A20)</x:f>
         <x:v>16</x:v>
       </x:c>
       <x:c r="E20" s="3"/>
       <x:c r="F20" s="3" t="str">
-        <x:v>HTTP/MQTT各核对1条新告警；MQTT加只读响应。</x:v>
+        <x:v>HTTP新告警；MQTT注册、心跳及只读请求应答。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="38" customHeight="1">
@@ -809,15 +809,15 @@
         <x:v>系统管理</x:v>
       </x:c>
       <x:c r="B21" s="3" t="n">
-        <x:f>COUNTIFS('主要用例'!B5:B32,A21)</x:f>
+        <x:f>COUNTIFS('主要用例'!B5:B33,A21)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C21" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!F5:F32,'主要用例'!B5:B32,A21)</x:f>
+        <x:f>SUMIFS('主要用例'!F5:F33,'主要用例'!B5:B33,A21)</x:f>
         <x:v>7</x:v>
       </x:c>
       <x:c r="D21" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!G5:G32,'主要用例'!B5:B32,A21)</x:f>
+        <x:f>SUMIFS('主要用例'!G5:G33,'主要用例'!B5:B33,A21)</x:f>
         <x:v>11</x:v>
       </x:c>
       <x:c r="E21" s="3"/>
@@ -830,15 +830,15 @@
         <x:v>必要补充</x:v>
       </x:c>
       <x:c r="B22" s="3" t="n">
-        <x:f>COUNTIFS('主要用例'!B5:B32,A22)</x:f>
+        <x:f>COUNTIFS('主要用例'!B5:B33,A22)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C22" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!F5:F32,'主要用例'!B5:B32,A22)</x:f>
+        <x:f>SUMIFS('主要用例'!F5:F33,'主要用例'!B5:B33,A22)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="D22" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!G5:G32,'主要用例'!B5:B32,A22)</x:f>
+        <x:f>SUMIFS('主要用例'!G5:G33,'主要用例'!B5:B33,A22)</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="E22" s="3"/>
@@ -851,15 +851,15 @@
         <x:v>收尾交付</x:v>
       </x:c>
       <x:c r="B23" s="3" t="n">
-        <x:f>COUNTIFS('主要用例'!B5:B32,A23)</x:f>
+        <x:f>COUNTIFS('主要用例'!B5:B33,A23)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="C23" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!F5:F32,'主要用例'!B5:B32,A23)</x:f>
+        <x:f>SUMIFS('主要用例'!F5:F33,'主要用例'!B5:B33,A23)</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="D23" s="3" t="n">
-        <x:f>SUMIFS('主要用例'!G5:G32,'主要用例'!B5:B32,A23)</x:f>
+        <x:f>SUMIFS('主要用例'!G5:G33,'主要用例'!B5:B33,A23)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="E23" s="3"/>
@@ -1266,7 +1266,7 @@
         <x:v>USB 摄像头发现、预览及运行算法</x:v>
       </x:c>
       <x:c r="D13" s="3" t="str">
-        <x:v>用户将 USB 摄像头接入被测盒子；开测前确认设备已识别、产品支持该输入，并记录设备节点或唯一标识。使用已就绪基础检测场景。</x:v>
+        <x:v>USB 摄像头为必测资源，现有硬件开测时核对设备枚举、标识和实时画面；使用已就绪基础检测场景。不得沿用历史“资源不足/暂不测试”跳过；异常需保存本轮证据。</x:v>
       </x:c>
       <x:c r="E13" s="3" t="str">
         <x:v>DUT;USB-CAMERA;MODEL-INVENTORY</x:v>
@@ -1773,10 +1773,10 @@
         <x:v>数据对接</x:v>
       </x:c>
       <x:c r="C28" s="8" t="str">
-        <x:v>MQTT 注册、业务响应和告警</x:v>
+        <x:v>MQTT 注册、心跳与业务响应</x:v>
       </x:c>
       <x:c r="D28" s="8" t="str">
-        <x:v>隔离Broker及订阅端可用；按当前协议确定topic、设备标识和心跳周期。</x:v>
+        <x:v>隔离 Broker 及订阅端可用；按当前控制协议确定 topic、设备标识和心跳周期。主动告警由 HTTP 推送，在 Q19 验证。</x:v>
       </x:c>
       <x:c r="E28" s="8" t="str">
         <x:v>DUT;MQTT-BROKER;PUSH-AUTHORIZATION</x:v>
@@ -1797,7 +1797,9 @@
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K28" s="15" t="str"/>
-      <x:c r="L28" s="15" t="str"/>
+      <x:c r="L28" s="15" t="str">
+        <x:v>v0.6：按已确认的 HTTP 告警、MQTT 控制设计修正预期；不要求 MQTT 主动发布告警。</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="44" customHeight="1">
       <x:c r="A29" s="3" t="str">
@@ -1934,6 +1936,40 @@
       </x:c>
       <x:c r="K32" s="15" t="str"/>
       <x:c r="L32" s="15" t="str"/>
+    </x:row>
+    <x:row r="33" ht="150" customHeight="1">
+      <x:c r="A33" s="8" t="str">
+        <x:v>Q29</x:v>
+      </x:c>
+      <x:c r="B33" s="8" t="str">
+        <x:v>事件与展示</x:v>
+      </x:c>
+      <x:c r="C33" s="8" t="str">
+        <x:v>事件上报大模型审核（本地模型与OpenAI接口）</x:v>
+      </x:c>
+      <x:c r="D33" s="8" t="str">
+        <x:v>使用FACE-VIDEO固定视频及人工可见的人物特征正负片段；本地VLM与OpenAI接口分别预检。审核由事件上报组件执行，普通行人检测产生候选，HTTP接收就绪。</x:v>
+      </x:c>
+      <x:c r="E33" s="8" t="str">
+        <x:v>DUT;FACE-VIDEO;MODEL-INVENTORY;VLM-MODEL;OPENAI-VLM;HTTP-RECEIVER;PUSH-AUTHORIZATION</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H33" s="8" t="str">
+        <x:v>停止并删除本轮视频任务、临时通道与复制场景；恢复原推送、审核参数和视频播放配置。保留原有业务及历史事件，不修改共享模型服务。</x:v>
+      </x:c>
+      <x:c r="I33" s="8" t="str">
+        <x:v>EVENT-012;EVENT-013;EVENT-014</x:v>
+      </x:c>
+      <x:c r="J33" s="15" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="K33" s="15"/>
+      <x:c r="L33" s="15"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="J5:J32">
@@ -1948,7 +1984,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re41452dbcac24286"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7eddc8026ba4afc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3926,13 +3962,13 @@
         <x:v>Q20-S03</x:v>
       </x:c>
       <x:c r="C87" s="3" t="str">
-        <x:v>触发一条新告警，从订阅端核对业务消息及媒体字段；恢复原配置。</x:v>
+        <x:v>核对只读设备信息响应中的业务结果；停止本轮订阅/请求，恢复原 MQTT 配置并刷新读回。</x:v>
       </x:c>
       <x:c r="D87" s="3" t="str">
-        <x:v>收到真实新告警且字段与事件中心一致；恢复配置可读回。</x:v>
+        <x:v>只读响应业务结果成功且内容与设备一致；原 MQTT 配置可读回。主动告警由 Q19 的 HTTP 闭环覆盖，不要求 MQTT 主动发布告警。</x:v>
       </x:c>
       <x:c r="E87" s="3" t="str">
-        <x:v>业务消息、事件ID和恢复证据。</x:v>
+        <x:v>只读业务响应、设备信息核对结果、恢复配置证据。</x:v>
       </x:c>
       <x:c r="F87" s="15" t="str"/>
       <x:c r="G87" s="15" t="str">
@@ -4216,6 +4252,167 @@
       </x:c>
       <x:c r="H99" s="15" t="str"/>
       <x:c r="I99" s="15" t="str"/>
+    </x:row>
+    <x:row r="100" ht="127.5" customHeight="1">
+      <x:c r="A100" s="3" t="str">
+        <x:v>Q29</x:v>
+      </x:c>
+      <x:c r="B100" s="3" t="str">
+        <x:v>Q29-S01</x:v>
+      </x:c>
+      <x:c r="C100" s="3" t="str">
+        <x:v>核对 FACE-VIDEO 固定视频和本地/接口两种审核资源；人工标注匹配与不匹配人物ROI、时间段。提示词可用“穿红色衣服的人”，缺红衣正例则选择实际可见特征。</x:v>
+      </x:c>
+      <x:c r="D100" s="3" t="str">
+        <x:v>正负事实可从当前目标裁剪图独立确认；未出现的特征不编造正例；两种模式分别记录资源与结果，缺一不影响另一模式可执行步骤。</x:v>
+      </x:c>
+      <x:c r="E100" s="3" t="str">
+        <x:v>视频哈希、片段/帧/目标框标注、提示词、本地模型及脱敏接口资源。</x:v>
+      </x:c>
+      <x:c r="F100" s="15"/>
+      <x:c r="G100" s="15" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="H100" s="15"/>
+      <x:c r="I100" s="15"/>
+    </x:row>
+    <x:row r="101" ht="127.5" customHeight="1">
+      <x:c r="A101" s="3" t="str">
+        <x:v>Q29</x:v>
+      </x:c>
+      <x:c r="B101" s="3" t="str">
+        <x:v>Q29-S02</x:v>
+      </x:c>
+      <x:c r="C101" s="3" t="str">
+        <x:v>复制行人检测/区域入侵场景，使用事件上报组件BA_00004；关闭审核，从相同起点重播正负片段建立基线。</x:v>
+      </x:c>
+      <x:c r="D101" s="3" t="str">
+        <x:v>正负候选均实际触发基线上报；固定ROI、告警间隔、去重和播放次数。独立VLM节点输出不能代替事件上报组件审核。</x:v>
+      </x:c>
+      <x:c r="E101" s="3" t="str">
+        <x:v>场景链、组件配置、候选目标/帧、基线事件与HTTP接收记录。</x:v>
+      </x:c>
+      <x:c r="F101" s="15"/>
+      <x:c r="G101" s="15" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="H101" s="15"/>
+      <x:c r="I101" s="15"/>
+    </x:row>
+    <x:row r="102" ht="127.5" customHeight="1">
+      <x:c r="A102" s="3" t="str">
+        <x:v>Q29</x:v>
+      </x:c>
+      <x:c r="B102" s="3" t="str">
+        <x:v>Q29-S03</x:v>
+      </x:c>
+      <x:c r="C102" s="3" t="str">
+        <x:v>开启本地模型审核，填写人物特征提示词并保存刷新；串行重播正负片段，逐目标对账审核日志、事件中心及HTTP接收。</x:v>
+      </x:c>
+      <x:c r="D102" s="3" t="str">
+        <x:v>本地模式真实执行：“是”对应事件放行，“否”有审核过滤证据且无该候选普通告警。不能以无检测或去重冒充审核过滤。</x:v>
+      </x:c>
+      <x:c r="E102" s="3" t="str">
+        <x:v>本地模式配置、目标裁剪图、审核结果、事件ID和HTTP对账。</x:v>
+      </x:c>
+      <x:c r="F102" s="15"/>
+      <x:c r="G102" s="15" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="H102" s="15"/>
+      <x:c r="I102" s="15"/>
+    </x:row>
+    <x:row r="103" ht="127.5" customHeight="1">
+      <x:c r="A103" s="3" t="str">
+        <x:v>Q29</x:v>
+      </x:c>
+      <x:c r="B103" s="3" t="str">
+        <x:v>Q29-S04</x:v>
+      </x:c>
+      <x:c r="C103" s="3" t="str">
+        <x:v>切换OpenAI兼容接口模式，按私有配置填写基地址、served-model-name与认证；保存刷新，按服务并发限制串行重播同一正负片段。</x:v>
+      </x:c>
+      <x:c r="D103" s="3" t="str">
+        <x:v>图像请求实际发往所配服务，“是”放行、“否”过滤；结果关联当前目标与帧，接口请求失败不当作否定判断。</x:v>
+      </x:c>
+      <x:c r="E103" s="3" t="str">
+        <x:v>脱敏模式/模型配置、服务图像请求应答、审核过滤记录和事件/HTTP关联。</x:v>
+      </x:c>
+      <x:c r="F103" s="15"/>
+      <x:c r="G103" s="15" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="H103" s="15"/>
+      <x:c r="I103" s="15"/>
+    </x:row>
+    <x:row r="104" ht="127.5" customHeight="1">
+      <x:c r="A104" s="3" t="str">
+        <x:v>Q29</x:v>
+      </x:c>
+      <x:c r="B104" s="3" t="str">
+        <x:v>Q29-S05</x:v>
+      </x:c>
+      <x:c r="C104" s="3" t="str">
+        <x:v>把同一目标的匹配提示词改成明显不匹配的衣着特征，保存刷新并停启任务，再重播同一片段；分别核对已测两种模式。</x:v>
+      </x:c>
+      <x:c r="D104" s="3" t="str">
+        <x:v>回读和实际审核使用新提示词；结果符合人工标注且不是上次缓存。同帧其他人的特征不替代当前目标。</x:v>
+      </x:c>
+      <x:c r="E104" s="3" t="str">
+        <x:v>修改前后提示词、停启与实际请求、目标ROI、判断及事件变化。</x:v>
+      </x:c>
+      <x:c r="F104" s="15"/>
+      <x:c r="G104" s="15" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="H104" s="15"/>
+      <x:c r="I104" s="15"/>
+    </x:row>
+    <x:row r="105" ht="127.5" customHeight="1">
+      <x:c r="A105" s="3" t="str">
+        <x:v>Q29</x:v>
+      </x:c>
+      <x:c r="B105" s="3" t="str">
+        <x:v>Q29-S06</x:v>
+      </x:c>
+      <x:c r="C105" s="3" t="str">
+        <x:v>仅在本轮接口配置中暂填无效API Key，触发一次审核；记录认证失败后恢复正确值并重播正负片段。</x:v>
+      </x:c>
+      <x:c r="D105" s="3" t="str">
+        <x:v>认证错误与模型否定分开记录；当前普通接口路径错误时降级放行并留日志，恢复后真实审核再次生效，其他业务不受影响。</x:v>
+      </x:c>
+      <x:c r="E105" s="3" t="str">
+        <x:v>脱敏认证错误、故障期事件、恢复配置及恢复后正负审核证据。</x:v>
+      </x:c>
+      <x:c r="F105" s="15"/>
+      <x:c r="G105" s="15" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="H105" s="15"/>
+      <x:c r="I105" s="15"/>
+    </x:row>
+    <x:row r="106" ht="127.5" customHeight="1">
+      <x:c r="A106" s="3" t="str">
+        <x:v>Q29</x:v>
+      </x:c>
+      <x:c r="B106" s="3" t="str">
+        <x:v>Q29-S07</x:v>
+      </x:c>
+      <x:c r="C106" s="3" t="str">
+        <x:v>关闭审核再重播原负例确认基线上报恢复；停止删除本轮任务、通道和复制场景，恢复原推送与参数。</x:v>
+      </x:c>
+      <x:c r="D106" s="3" t="str">
+        <x:v>关闭审核后恢复原上报规则；两种模式结果分别留证。清理不影响原业务，不修改或停止共享模型服务。</x:v>
+      </x:c>
+      <x:c r="E106" s="3" t="str">
+        <x:v>开关关闭后的事件、两种模式结论及清理恢复清单。</x:v>
+      </x:c>
+      <x:c r="F106" s="15"/>
+      <x:c r="G106" s="15" t="str">
+        <x:v>未执行</x:v>
+      </x:c>
+      <x:c r="H106" s="15"/>
+      <x:c r="I106" s="15"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
@@ -4225,7 +4422,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2b7724b3fd145c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb366a5cee4e7479d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4488,7 +4685,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a34ebdf0ecb49ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1fa59185af24369"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4530,21 +4727,21 @@
         <x:v>评审意见</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="44" customHeight="1">
+    <x:row r="5" ht="60" customHeight="1">
       <x:c r="A5" s="3" t="str">
         <x:v>耗时口径</x:v>
       </x:c>
       <x:c r="B5" s="3" t="str">
-        <x:v>141–232分钟为初始估算，约2小时21分至3小时52分；尚未用此版计时实跑。模型导入与首次初始化、首次配置、部署服务、完整包校验、下载、重试和排障另计。</x:v>
+        <x:v>157–260分钟为设计估算，尚未用此版计时实跑。首次模型初始化、配置、服务部署、下载、重试及排障另计。</x:v>
       </x:c>
       <x:c r="C5" s="15" t="str"/>
     </x:row>
-    <x:row r="6" ht="36" customHeight="1">
+    <x:row r="6" ht="60" customHeight="1">
       <x:c r="A6" s="8" t="str">
         <x:v>提速方式</x:v>
       </x:c>
       <x:c r="B6" s="8" t="str">
-        <x:v>复用短视频、场景、底库和事件；按接入方式逐路串行；控制素材和模型大小；不再展开327条全量用例及其参数/接口矩阵。</x:v>
+        <x:v>复用短视频、场景、底库和事件；接入方式与审核模式逐项串行；不展开331条全量用例及其矩阵。</x:v>
       </x:c>
       <x:c r="C6" s="15" t="str"/>
     </x:row>
@@ -4557,12 +4754,12 @@
       </x:c>
       <x:c r="C7" s="15" t="str"/>
     </x:row>
-    <x:row r="8" ht="44" customHeight="1">
+    <x:row r="8" ht="60" customHeight="1">
       <x:c r="A8" s="8" t="str">
         <x:v>执行顺序</x:v>
       </x:c>
       <x:c r="B8" s="8" t="str">
-        <x:v>Q01准备；Q02–Q03资源管理；Q04–Q08和Q25输入；Q09–Q10任务；Q11–Q16识别与图片；Q26–Q27大模型；Q17/Q28/Q18事件与大屏；Q19–Q20推送；Q21–Q24系统及收尾。</x:v>
+        <x:v>Q01准备；Q02–Q03资源；Q04–Q08和Q25输入；Q09–Q10任务；Q11–Q16识别与图片；Q26–Q27大模型；Q29事件上报审核；Q17/Q28/Q18事件展示；Q19–Q20推送；Q21–Q24收尾。</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str"/>
     </x:row>
@@ -4593,12 +4790,12 @@
       </x:c>
       <x:c r="C11" s="15" t="str"/>
     </x:row>
-    <x:row r="12" ht="44" customHeight="1">
+    <x:row r="12" ht="60" customHeight="1">
       <x:c r="A12" s="8" t="str">
         <x:v>精度边界</x:v>
       </x:c>
       <x:c r="B12" s="8" t="str">
-        <x:v>VLM 与 DINO 用人工可见的正负固定样本判定基本功能，不宣称精度达标；USB、VLM、DINO 已纳入必测，缺可运行模型记阻塞。其他无模型场景、音柱和授权验收仍排除。</x:v>
+        <x:v>VLM、DINO及事件上报审核用人工可见正负样本验证基本功能，不宣称精度达标。USB必测；本地/接口审核独立记录，缺项只阻塞对应步骤。</x:v>
       </x:c>
       <x:c r="C12" s="15" t="str"/>
     </x:row>
@@ -4611,30 +4808,30 @@
       </x:c>
       <x:c r="C13" s="15" t="str"/>
     </x:row>
-    <x:row r="14" ht="36" customHeight="1">
+    <x:row r="14" ht="60" customHeight="1">
       <x:c r="A14" s="8" t="str">
         <x:v>与全量库关系</x:v>
       </x:c>
       <x:c r="B14" s="8" t="str">
-        <x:v>全量库版本1.4.0；“主要用例”按编号保留来源映射，覆盖范围经过裁剪，不能把快速通过回填为原全量用例通过。</x:v>
+        <x:v>全量库版本1.6.0；保留编号来源映射，快速通过不回填全量用例通过。</x:v>
       </x:c>
       <x:c r="C14" s="15" t="str"/>
     </x:row>
-    <x:row r="15" ht="36" customHeight="1">
+    <x:row r="15" ht="60" customHeight="1">
       <x:c r="A15" s="3" t="str">
         <x:v>实施状态</x:v>
       </x:c>
       <x:c r="B15" s="3" t="str">
-        <x:v>此文件是独立评审稿，尚未接入customer_journey.py执行队列。评审确认后实现quick模式，仍复用资源包和逐步记录机制。</x:v>
+        <x:v>正式快测用例库，已接入customer_journey.py；每轮冻结副本，执行结果另存。</x:v>
       </x:c>
       <x:c r="C15" s="15" t="str"/>
     </x:row>
-    <x:row r="16" ht="36" customHeight="1">
+    <x:row r="16" ht="60" customHeight="1">
       <x:c r="A16" s="8" t="str">
         <x:v>评审决策1</x:v>
       </x:c>
       <x:c r="B16" s="8" t="str">
-        <x:v>默认采用28条/约2小时21分至3小时52分是否合适？更短预算应明确减少范围，不能隐去协议或模块。</x:v>
+        <x:v>当前29条核心用例，预计157–260分钟；若减少范围须明确列出未执行项。</x:v>
       </x:c>
       <x:c r="C16" s="15" t="str"/>
     </x:row>
@@ -4674,12 +4871,12 @@
       </x:c>
       <x:c r="C20" s="15" t="str"/>
     </x:row>
-    <x:row r="21" ht="44" customHeight="1">
+    <x:row r="21" ht="60" customHeight="1">
       <x:c r="A21" s="3" t="str">
         <x:v>USB资源</x:v>
       </x:c>
       <x:c r="B21" s="3" t="str">
-        <x:v>USB-CAMERA 为外接硬件，不需要复制进素材包；资源配置已取消旧排除，预检提示待核实，正式开测以盒子端枚举和画面为准。</x:v>
+        <x:v>USB-CAMERA 已纳入必测，硬件资源就绪状态维护在私有配置。每轮仍核对设备列表、实时画面、算法输出和启停恢复；旧缺口不构成本轮免测依据。</x:v>
       </x:c>
       <x:c r="C21" s="15" t="str"/>
     </x:row>
@@ -4692,12 +4889,12 @@
       </x:c>
       <x:c r="C22" s="15" t="str"/>
     </x:row>
-    <x:row r="23" ht="44" customHeight="1">
+    <x:row r="23" ht="60" customHeight="1">
       <x:c r="A23" s="3" t="str">
         <x:v>大模型资源</x:v>
       </x:c>
       <x:c r="B23" s="3" t="str">
-        <x:v>VLM-MODEL 与 DINO-MODEL 分别预检。现有 BM1688 GroundingDINO 包是候选；Qwen 原始 bmodel/配置尚不能证明可导入。开测前记录模型包、词表/分词器、设备加载状态、正负样本哈希及提示词；缺项只阻塞 Q26/Q27 对应项。</x:v>
+        <x:v>本地VLM、DINO与OPENAI-VLM分别预检；接口审核核对实际served-model-name、认证、图像输入和并发限制。资源地址、模型与密钥放私有配置，缺项只影响对应模式。</x:v>
       </x:c>
       <x:c r="C23" s="15" t="str"/>
     </x:row>
@@ -4719,19 +4916,19 @@
       </x:c>
       <x:c r="C25" s="15" t="str"/>
     </x:row>
-    <x:row r="26" ht="44" customHeight="1">
+    <x:row r="26" ht="60" customHeight="1">
       <x:c r="A26" s="8" t="str">
         <x:v>资料来源</x:v>
       </x:c>
       <x:c r="B26" s="8" t="str">
-        <x:v>仓库test/customer-journey/CosmoEdge-客户旅程测试用例.xlsx（1.4.0）及其suite.json；用户本次范围和此前明确排除项。</x:v>
+        <x:v>正式全量用例库1.6.0、当前组件实现与用户确认的USB必测、固定视频及接口审核范围。</x:v>
       </x:c>
       <x:c r="C26" s="15" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31a6607c72a14748"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca257cbc92b142c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/test/customer-journey/CosmoEdge-主要功能客户旅程测试用例.xlsx
+++ b/test/customer-journey/CosmoEdge-主要功能客户旅程测试用例.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="评审总览" sheetId="1" r:id="R4e2e12dec86c44b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要用例" sheetId="2" r:id="Reb05f24b4b734d80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="步骤与验收" sheetId="3" r:id="R23f294e649194cb2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="按需补测" sheetId="4" r:id="Ra763ecfcb5974a60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="范围与评审" sheetId="5" r:id="R9023807993d24ff5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="评审总览" sheetId="1" r:id="R01543374d3264a01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要用例" sheetId="2" r:id="Rd6611126b8a44e7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="步骤与验收" sheetId="3" r:id="Rf18455718b9642e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="按需补测" sheetId="4" r:id="Raceafb6590e74d11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="范围与评审" sheetId="5" r:id="R682e7dd91ba9449b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -472,7 +472,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="16" t="str">
-        <x:v>v0.7 已确认快测用例 · 2026-10-19 · 用例定义，实测结果另存</x:v>
+        <x:v>v0.8 已确认快测用例 · 2026-10-19 · 用例定义，实测结果另存</x:v>
       </x:c>
       <x:c r="B3" s="3"/>
       <x:c r="C3" s="3"/>
@@ -533,7 +533,7 @@
       </x:c>
       <x:c r="B7" s="3" t="n">
         <x:f>SUM('主要用例'!F5:F33)</x:f>
-        <x:v>157</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C7" s="3"/>
       <x:c r="D7" s="3" t="str">
@@ -553,7 +553,7 @@
       </x:c>
       <x:c r="B8" s="3" t="n">
         <x:f>SUM('主要用例'!G5:G33)</x:f>
-        <x:v>260</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C8" s="3"/>
       <x:c r="D8" s="3" t="str">
@@ -730,11 +730,11 @@
       </x:c>
       <x:c r="C17" s="3" t="n">
         <x:f>SUMIFS('主要用例'!F5:F33,'主要用例'!B5:B33,A17)</x:f>
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D17" s="3" t="n">
         <x:f>SUMIFS('主要用例'!G5:G33,'主要用例'!B5:B33,A17)</x:f>
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E17" s="3"/>
       <x:c r="F17" s="3" t="str">
@@ -1459,7 +1459,7 @@
       <x:c r="K18" s="15" t="str"/>
       <x:c r="L18" s="15" t="str"/>
     </x:row>
-    <x:row r="19" ht="44" customHeight="1">
+    <x:row r="19" ht="65" customHeight="1">
       <x:c r="A19" s="3" t="str">
         <x:v>Q14</x:v>
       </x:c>
@@ -1470,28 +1470,30 @@
         <x:v>单图、批量图片和临时参数</x:v>
       </x:c>
       <x:c r="D19" s="3" t="str">
-        <x:v>选2张可解码、目标清晰的图片；Q03 图片场景可用，或使用已存在的等价测试场景。</x:v>
+        <x:v>选2张可解码、目标清晰的图片；Q03图片场景可用。核对模型类别，准备分值介于0和1的稳定目标用于阈值对照；OBB已部署时优先抽样，专项另执行ALG-38874。</x:v>
       </x:c>
       <x:c r="E19" s="3" t="str">
-        <x:v>DUT;IMAGE-MEDIA</x:v>
+        <x:v>DUT;IMAGE-MEDIA;MODEL-INVENTORY</x:v>
       </x:c>
       <x:c r="F19" s="13" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G19" s="13" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H19" s="3" t="str">
         <x:v>清空本轮图片及临时设置；任务按页面/接口生命周期释放。</x:v>
       </x:c>
       <x:c r="I19" s="3" t="str">
-        <x:v>IMAGE-001;IMAGE-002;IMAGE-003;IMAGE-011;SCENE-010</x:v>
+        <x:v>IMAGE-001;IMAGE-002;IMAGE-003;IMAGE-011;SCENE-010;IMAGE-007;ALG-38874</x:v>
       </x:c>
       <x:c r="J19" s="15" t="str">
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="K19" s="15" t="str"/>
-      <x:c r="L19" s="15" t="str"/>
+      <x:c r="L19" s="15" t="str">
+        <x:v>v0.8补充旧字段与直接阈值对照；这里只抽样，不能替代ALG-38874全项验收。</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="44" customHeight="1">
       <x:c r="A20" s="8" t="str">
@@ -1984,7 +1986,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7eddc8026ba4afc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60c143b7df11423f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3195,7 +3197,7 @@
       <x:c r="H53" s="15" t="str"/>
       <x:c r="I53" s="15" t="str"/>
     </x:row>
-    <x:row r="54" ht="36" customHeight="1">
+    <x:row r="54" ht="50" customHeight="1">
       <x:c r="A54" s="8" t="str">
         <x:v>Q14</x:v>
       </x:c>
@@ -3203,13 +3205,13 @@
         <x:v>Q14-S01</x:v>
       </x:c>
       <x:c r="C54" s="8" t="str">
-        <x:v>选择图片场景，上传1张图片并提交分析。</x:v>
+        <x:v>选择图片场景，检查参数面板和编排，再上传1张图片提交分析。</x:v>
       </x:c>
       <x:c r="D54" s="8" t="str">
-        <x:v>场景可选；输出目标/业务结果与当前图片对应；结果未沿用旧图片。</x:v>
+        <x:v>无视频区域/布防配置和无效置信度偏移；直接置信度阈值可用。输出与当前图片对应；若为OBB，核对旋转框和原图，不沿用旧结果。</x:v>
       </x:c>
       <x:c r="E54" s="8" t="str">
-        <x:v>输入哈希、场景ID、结果和标注图。</x:v>
+        <x:v>参数与编排截图、输入哈希、场景及模型标识、原始结果与标注图。</x:v>
       </x:c>
       <x:c r="F54" s="15" t="str"/>
       <x:c r="G54" s="15" t="str">
@@ -3241,7 +3243,7 @@
       <x:c r="H55" s="15" t="str"/>
       <x:c r="I55" s="15" t="str"/>
     </x:row>
-    <x:row r="56" ht="44" customHeight="1">
+    <x:row r="56" ht="65" customHeight="1">
       <x:c r="A56" s="8" t="str">
         <x:v>Q14</x:v>
       </x:c>
@@ -3249,13 +3251,13 @@
         <x:v>Q14-S03</x:v>
       </x:c>
       <x:c r="C56" s="8" t="str">
-        <x:v>修改1个临时分析参数并提交；刷新或新开同场景，检查默认值。</x:v>
+        <x:v>记录稳定目标分值，用其两侧的直接置信度阈值重测同一图；刷新检查默认值。保存并重新打开场景，再检查参数声明。</x:v>
       </x:c>
       <x:c r="D56" s="8" t="str">
-        <x:v>临时值参与本次分析；场景/任务默认值未被永久改写；再次分析可用。</x:v>
+        <x:v>低阈值保留、高阈值过滤同一目标；临时值不改默认，保存重开不恢复旧字段。缺边界样本明确记录缺口；不能只以请求成功判定阈值生效。</x:v>
       </x:c>
       <x:c r="E56" s="8" t="str">
-        <x:v>临时请求、默认值和再次分析结果。</x:v>
+        <x:v>同一目标两次阈值、请求与返回对照；默认值回读；保存重开后的参数截图。</x:v>
       </x:c>
       <x:c r="F56" s="15" t="str"/>
       <x:c r="G56" s="15" t="str">
@@ -4422,7 +4424,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb366a5cee4e7479d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd415d8ce9c89455f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4685,7 +4687,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1fa59185af24369"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e23897c5a7e4053"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4928,7 +4930,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca257cbc92b142c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95389c2c329e48b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>